--- a/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TNB2_B4_78</t>
+    <t>TNB2B178</t>
   </si>
   <si>
     <t>Biên bản số</t>
@@ -47,7 +47,7 @@
     <t>Đường kính</t>
   </si>
   <si>
-    <t>1200 mm</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>

--- a/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
@@ -23,13 +23,13 @@
     <t>Hạng mục</t>
   </si>
   <si>
+    <t>Thi công cọc khoan nhồi</t>
+  </si>
+  <si>
+    <t>Tên bộ phận</t>
+  </si>
+  <si>
     <t>Khách sạn Grand Hyatt</t>
-  </si>
-  <si>
-    <t>Tên bộ phận</t>
-  </si>
-  <si>
-    <t>Thi công cọc khoan nhồi</t>
   </si>
   <si>
     <t>Số hiệu cọc</t>

--- a/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="128">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Khu đô thị du lịch lấn biển Cần Giờ</t>
+    <t>Cần Giờ</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>TNB2B178</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGCT-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -119,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét pha - cát pha màu xám xanh, xám đen, trạng thái dẻo chảy đến chảy</t>
+    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo mềm, dẻo chảy đến chảy</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -178,7 +178,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét pha màu xám xanh, xám đen, trạng thái dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">20:10
@@ -253,7 +253,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét - Sét pha màu xám xanh, xám ghi, xám vàng, nâu đỏ, trạng thái dẻo cứng đến nửa cứng</t>
+    <t>Sét pha, xám xanh, xám đen, xám ghi, xám vàng, nâu đỏ, TT dẻo cứng đến nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">21:40
@@ -273,7 +273,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát hạt mịn màu xám ghi, xám vàng, kết cấu chặt đến rất chặt</t>
+    <t>Cát mịn đến hạt vừa, màu xám ghi, xám vàng, đôi chỗ kẹp sét pha, kết cấu chặt vừa đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">22:10
@@ -432,6 +432,9 @@
   </si>
   <si>
     <t>TỔNG CỘNG</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -3020,10 +3023,10 @@
         <v>126</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="D10" s="33">
         <v>37</v>

--- a/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TNB2B178</t>
+    <t>TN-B2-B1.78</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/26fb8f1a-7f35-4f3e-a03c-ae0d837e986d_Thi_công_cọc_khoan_nhồi_TNB2_B4_78_1200_mm_17-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi</t>
+    <t>Khách sạn GrandHyatt</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TN-B2-B1.78</t>
+    <t>B1.78</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -119,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo mềm, dẻo chảy đến chảy</t>
+    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo chảy đến chảy</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -356,7 +356,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sét pha màu xám xanh, xám đen, trạng thái nửa cứng đến cứng</t>
+    <t>Sét pha, xám xanh, xám đen, trạng thái nửa cứng đến cứng</t>
   </si>
   <si>
     <t xml:space="preserve">01:50
